--- a/artfynd/A 44809-2021 artfynd.xlsx
+++ b/artfynd/A 44809-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44809-2021 artfynd.xlsx
+++ b/artfynd/A 44809-2021 artfynd.xlsx
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60212345</v>
+        <v>96145278</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjögerås S, Dls</t>
+          <t>Herrkaserud, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345289.073952738</v>
+        <v>345458</v>
       </c>
       <c r="R2" t="n">
-        <v>6542771.676646371</v>
+        <v>6543061</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,66 +756,79 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96142846</v>
+        <v>96142859</v>
       </c>
       <c r="B3" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Herrkaserud, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345540.5994607728</v>
+        <v>345483</v>
       </c>
       <c r="R3" t="n">
-        <v>6543205.109316632</v>
+        <v>6542487</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,27 +858,18 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,16 +891,11 @@
         <v>96142867</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -931,12 +908,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345626.8232333382</v>
+        <v>345627</v>
       </c>
       <c r="R4" t="n">
-        <v>6542265.967567307</v>
+        <v>6542266</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +959,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,56 +989,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96142859</v>
+        <v>96604641</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herrkaserud, Dls</t>
+          <t>Herrkaserud norr, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345483.2631156445</v>
+        <v>345502</v>
       </c>
       <c r="R5" t="n">
-        <v>6542486.855990836</v>
+        <v>6542266</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,34 +1080,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96145278</v>
+        <v>96604646</v>
       </c>
       <c r="B6" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,37 +1109,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Herrkaserud, Dls</t>
+          <t>Herrkaserud norr, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345457.3141438399</v>
+        <v>345502</v>
       </c>
       <c r="R6" t="n">
-        <v>6543061.473123645</v>
+        <v>6542266</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,22 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,46 +1191,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96604646</v>
+        <v>60212345</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,16 +1218,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1298,32 +1235,27 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herrkaserud norr, Dls</t>
+          <t>Sjögerås S, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>345502.249821632</v>
+        <v>345289</v>
       </c>
       <c r="R7" t="n">
-        <v>6542265.305625195</v>
+        <v>6542772</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,22 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,12 +1299,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1392,12 +1314,7 @@
         <v>96604648</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345502.249821632</v>
+        <v>345502</v>
       </c>
       <c r="R8" t="n">
-        <v>6542265.305625195</v>
+        <v>6542266</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1474,19 +1391,9 @@
           <t>2021-10-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,15 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96142860</v>
+        <v>96142846</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345489.3944713696</v>
+        <v>345541</v>
       </c>
       <c r="R9" t="n">
-        <v>6542497.957604073</v>
+        <v>6543205</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,19 +1488,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,15 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96142856</v>
+        <v>96142849</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>345479.8995769444</v>
+        <v>345634</v>
       </c>
       <c r="R10" t="n">
-        <v>6542595.83222825</v>
+        <v>6543114</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,19 +1585,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,15 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96142849</v>
+        <v>96142856</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>345633.5793396647</v>
+        <v>345480</v>
       </c>
       <c r="R11" t="n">
-        <v>6543114.721433708</v>
+        <v>6542596</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1810,19 +1682,9 @@
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,65 +1711,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96604641</v>
+        <v>96142860</v>
       </c>
       <c r="B12" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Herrkaserud norr, Dls</t>
+          <t>Herrkaserud, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345502.249821632</v>
+        <v>345489</v>
       </c>
       <c r="R12" t="n">
-        <v>6542265.305625195</v>
+        <v>6542498</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,22 +1776,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,12 +1796,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 44809-2021 artfynd.xlsx
+++ b/artfynd/A 44809-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96145278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96604641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96604646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60212345</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96604648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142846</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142849</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142856</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,8 +1860,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96142860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>